--- a/link-semantics/interim/Link_Kind_Audit.xlsx
+++ b/link-semantics/interim/Link_Kind_Audit.xlsx
@@ -31,13 +31,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,7 +51,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -56,12 +59,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,62 +443,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>link_kind</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>provenance</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>statement</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>file</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>sheet</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>subject_cols</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>object_col</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>distinct_subjects</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>distinct_objects</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>object_missing</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>justification_col</t>
         </is>
@@ -629,13 +641,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5885</v>
+        <v>5988</v>
       </c>
       <c r="I4" t="n">
-        <v>5868</v>
+        <v>5969</v>
       </c>
       <c r="J4" t="n">
-        <v>5885</v>
+        <v>5988</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -729,13 +741,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>17607</v>
+        <v>17742</v>
       </c>
       <c r="I6" t="n">
         <v>295</v>
       </c>
       <c r="J6" t="n">
-        <v>12747</v>
+        <v>12833</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1229,13 +1241,13 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I16" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J16" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1283,13 +1295,13 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="I17" t="n">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="J17" t="n">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1387,10 +1399,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="I19" t="n">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="J19" t="n">
         <v>3</v>
@@ -1415,22 +1427,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>suffix</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>result_variable</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>variables</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>dss</t>
         </is>
@@ -1707,32 +1719,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>suffix</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ct_bound</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>assigned</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>value_list</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>assigned_rate</t>
         </is>
@@ -3249,17 +3261,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>tokens</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>uses</t>
         </is>
@@ -3332,22 +3344,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>bc_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>uses</t>
         </is>
@@ -10640,12 +10652,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>check</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
@@ -10658,7 +10670,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -10686,12 +10698,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -10724,7 +10736,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5885</v>
+        <v>5988</v>
       </c>
     </row>
     <row r="5">
@@ -10744,7 +10756,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17607</v>
+        <v>17742</v>
       </c>
     </row>
     <row r="7">
@@ -10844,7 +10856,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17">
@@ -10854,7 +10866,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="18">
@@ -10874,7 +10886,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="20">
@@ -10914,7 +10926,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13686</v>
+        <v>13789</v>
       </c>
     </row>
     <row r="24">
@@ -10924,7 +10936,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25">
@@ -10934,7 +10946,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26">
@@ -10954,7 +10966,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="28">
@@ -10964,7 +10976,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17607</v>
+        <v>17742</v>
       </c>
     </row>
     <row r="29">
@@ -11354,7 +11366,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -11382,22 +11394,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>link_kind</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>provenance</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>entries</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
@@ -11472,7 +11484,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>13686</v>
+        <v>13789</v>
       </c>
     </row>
     <row r="6">
@@ -11490,7 +11502,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
@@ -11508,7 +11520,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8">
@@ -11544,7 +11556,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="10">
@@ -11562,7 +11574,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>17607</v>
+        <v>17742</v>
       </c>
     </row>
     <row r="11">
@@ -11616,12 +11628,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>codelists</t>
         </is>
@@ -11644,7 +11656,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4">
@@ -11654,7 +11666,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -11682,27 +11694,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>system_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>distinct_codes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>distinct_bcs</t>
         </is>
@@ -11744,12 +11756,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -11880,12 +11892,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>pin</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -11899,7 +11911,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7fc7d1f719d7aa287703ac11d03a1c07d4e334fe</t>
+          <t>c8ef6279d51d7f5e293c0d4984336aeda8f6d3b8</t>
         </is>
       </c>
     </row>
@@ -11947,7 +11959,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -11959,7 +11971,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-04-09 09:35:38</t>
+          <t>2026-09-30 18:19:16</t>
         </is>
       </c>
     </row>
@@ -11971,7 +11983,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-04-19 21:58:30</t>
+          <t>2026-09-30 18:19:26</t>
         </is>
       </c>
     </row>
@@ -11983,7 +11995,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-02 15:56</t>
+          <t>2026-09-30 18:19</t>
         </is>
       </c>
     </row>
@@ -12002,32 +12014,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variables</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>dss</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>with_subset_codelist</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>values_total</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>distinct_values</t>
         </is>
@@ -12114,12 +12126,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -12220,32 +12232,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>codelist_concept_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>value_list</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>variables</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>named</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>names</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>naming</t>
         </is>

--- a/link-semantics/interim/Link_Kind_Audit.xlsx
+++ b/link-semantics/interim/Link_Kind_Audit.xlsx
@@ -11911,7 +11911,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>c8ef6279d51d7f5e293c0d4984336aeda8f6d3b8</t>
+          <t>c3549da46c92a9ff191f6ccb46706922955bebfd</t>
         </is>
       </c>
     </row>
@@ -11971,7 +11971,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-30 18:19:16</t>
+          <t>2026-10-01 10:39:19</t>
         </is>
       </c>
     </row>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-30 18:19:26</t>
+          <t>2026-10-01 10:39:28</t>
         </is>
       </c>
     </row>
@@ -11995,7 +11995,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-30 18:19</t>
+          <t>2026-10-01 10:39</t>
         </is>
       </c>
     </row>

--- a/link-semantics/interim/Link_Kind_Audit.xlsx
+++ b/link-semantics/interim/Link_Kind_Audit.xlsx
@@ -31,16 +31,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -51,7 +48,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -59,21 +56,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,62 +431,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>link_kind</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>provenance</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>statement</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>file</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>sheet</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>subject_cols</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>object_col</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>distinct_subjects</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>distinct_objects</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>object_missing</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>justification_col</t>
         </is>
@@ -1241,13 +1229,13 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>260</v>
+        <v>363</v>
       </c>
       <c r="I16" t="n">
-        <v>260</v>
+        <v>363</v>
       </c>
       <c r="J16" t="n">
-        <v>260</v>
+        <v>363</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1427,22 +1415,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>suffix</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>result_variable</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>variables</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>dss</t>
         </is>
@@ -1719,32 +1707,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>suffix</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ct_bound</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>assigned</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>value_list</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>assigned_rate</t>
         </is>
@@ -3261,17 +3249,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tokens</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>uses</t>
         </is>
@@ -3344,22 +3332,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>bc_id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>uses</t>
         </is>
@@ -10652,12 +10640,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>check</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
@@ -10698,12 +10686,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -10856,7 +10844,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>260</v>
+        <v>363</v>
       </c>
     </row>
     <row r="17">
@@ -10936,7 +10924,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>261</v>
+        <v>364</v>
       </c>
     </row>
     <row r="25">
@@ -11394,22 +11382,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>link_kind</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>provenance</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>entries</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
@@ -11502,7 +11490,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>261</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7">
@@ -11624,16 +11612,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>codelists</t>
         </is>
@@ -11642,41 +11630,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>class-category-term</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>206</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UNMATCHED</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>suffix-strip</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>normalized</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -11694,27 +11662,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>system_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distinct_codes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>distinct_bcs</t>
         </is>
@@ -11756,12 +11724,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -11892,12 +11860,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>pin</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -11911,7 +11879,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>c3549da46c92a9ff191f6ccb46706922955bebfd</t>
+          <t>e2ecb6d75acc3d988e7cb1cb00f29230350409a3</t>
         </is>
       </c>
     </row>
@@ -11983,7 +11951,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-01 10:39:28</t>
+          <t>2026-10-08 11:01:50</t>
         </is>
       </c>
     </row>
@@ -12014,32 +11982,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>variables</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>dss</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>with_subset_codelist</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>values_total</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>distinct_values</t>
         </is>
@@ -12126,12 +12094,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -12232,32 +12200,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>codelist_concept_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value_list</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>variables</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>named</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>names</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>naming</t>
         </is>
